--- a/treasury-cashflow-simulation/data/setup.xlsx
+++ b/treasury-cashflow-simulation/data/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mis cosas\Coding\Proyectos IA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mis cosas\Coding\Work_Portfolio\treasury-cashflow-simulation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349DDB39-4B1B-43A1-880A-CC3CD9C41760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032B6CA7-150B-4693-A21A-80012B2CB051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="-90" windowWidth="19380" windowHeight="12180" activeTab="1" xr2:uid="{8882FF45-AD47-4D8B-9BA7-5A0D5C83F790}"/>
+    <workbookView xWindow="19110" yWindow="-90" windowWidth="19380" windowHeight="12180" xr2:uid="{8882FF45-AD47-4D8B-9BA7-5A0D5C83F790}"/>
   </bookViews>
   <sheets>
     <sheet name="Static_Data_Bank_Accounts" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
   <si>
     <t>account_number</t>
   </si>
@@ -98,13 +98,25 @@
     <t>bank_4</t>
   </si>
   <si>
-    <t>Month-End</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>Frequent</t>
+    <t>Incoming cash</t>
+  </si>
+  <si>
+    <t>Outgoing cash</t>
+  </si>
+  <si>
+    <t>Bank fees</t>
+  </si>
+  <si>
+    <t>Month-end interest</t>
+  </si>
+  <si>
+    <t>Internal Sweep</t>
+  </si>
+  <si>
+    <t>Treasury</t>
+  </si>
+  <si>
+    <t>Cash sweep between accounts</t>
   </si>
 </sst>
 </file>
@@ -1145,12 +1157,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E51495B-C84D-49AD-A1BC-E3B5BC3C01AB}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -1166,10 +1178,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -1177,10 +1189,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
@@ -1188,10 +1200,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -1199,13 +1211,24 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
